--- a/Result/profitability/3042.xlsx
+++ b/Result/profitability/3042.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>1.335</v>
+        <v>1.35125</v>
       </c>
       <c r="N2" t="n">
-        <v>32.45375</v>
+        <v>32.22375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.89</v>
       </c>
       <c r="M3" t="n">
-        <v>1.25875</v>
+        <v>1.245</v>
       </c>
       <c r="N3" t="n">
-        <v>31.3675</v>
+        <v>31.25625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>1.03</v>
       </c>
       <c r="M4" t="n">
-        <v>1.17</v>
+        <v>1.20125</v>
       </c>
       <c r="N4" t="n">
-        <v>30.5375</v>
+        <v>30.2525</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.96</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1175</v>
+        <v>1.18625</v>
       </c>
       <c r="N5" t="n">
-        <v>29.83375</v>
+        <v>29.77125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.26</v>
       </c>
       <c r="M6" t="n">
-        <v>1.015</v>
+        <v>1.0325</v>
       </c>
       <c r="N6" t="n">
-        <v>28.08375</v>
+        <v>28.32625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.63</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9075</v>
+        <v>0.94625</v>
       </c>
       <c r="N7" t="n">
-        <v>27.08125</v>
+        <v>27.1975</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.92</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8575</v>
+        <v>0.89625</v>
       </c>
       <c r="N8" t="n">
-        <v>26.30875</v>
+        <v>26.40625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3699</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2474</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1225</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.11</v>
+      </c>
+      <c r="G75" t="n">
+        <v>622</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.82%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>48</v>
+      </c>
+      <c r="J75" t="n">
+        <v>670</v>
+      </c>
+      <c r="K75" t="n">
+        <v>555</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.4325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.3425</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3099999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2348484848484846</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.7800000000000011</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.02412619857717302</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5499999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5092592592592591</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01487652484379653</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
